--- a/public/mau-lich-su-gia.xlsx
+++ b/public/mau-lich-su-gia.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Du lieu" sheetId="1" r:id="rId1"/>
+    <sheet name="lich-su-gia" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -29,7 +29,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFF3F0E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -57,17 +57,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -140,7 +138,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -162,7 +160,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -184,7 +182,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -206,7 +204,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -228,7 +226,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -250,7 +248,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -272,7 +270,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -294,7 +292,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -492,7 +490,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -514,7 +512,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -536,7 +534,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -558,7 +556,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -580,7 +578,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -602,7 +600,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -624,7 +622,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -646,7 +644,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -663,12 +661,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -685,12 +683,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -707,12 +705,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -729,12 +727,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -751,12 +749,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -773,12 +771,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -795,12 +793,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -817,12 +815,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -844,7 +842,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -866,7 +864,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -888,7 +886,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -910,7 +908,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -932,7 +930,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -954,7 +952,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -976,7 +974,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -998,7 +996,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1020,12 +1018,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1042,12 +1040,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1064,12 +1062,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1086,12 +1084,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1108,12 +1106,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1130,12 +1128,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1152,12 +1150,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1174,12 +1172,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1191,12 +1189,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1213,12 +1211,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1235,12 +1233,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1257,12 +1255,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1279,12 +1277,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1301,12 +1299,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1323,12 +1321,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1345,12 +1343,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đà Nẵng</t>
+          <t xml:space="preserve">Huế</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1548,12 +1546,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1570,12 +1568,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -1592,12 +1590,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1614,12 +1612,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -1636,12 +1634,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -1658,12 +1656,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -1680,12 +1678,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -1702,12 +1700,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Văn phòng</t>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">thue</t>
+          <t xml:space="preserve">ban</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -1724,7 +1722,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -1746,7 +1744,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1768,7 +1766,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -1790,7 +1788,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -1812,7 +1810,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -1834,7 +1832,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -1856,7 +1854,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -1878,7 +1876,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Nhà mặt phố</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -1900,7 +1898,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -1922,7 +1920,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -1944,7 +1942,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -1966,7 +1964,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -1988,7 +1986,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2010,7 +2008,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2032,7 +2030,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2054,7 +2052,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Nhà riêng</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2076,7 +2074,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2098,7 +2096,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2120,7 +2118,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2142,7 +2140,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2164,7 +2162,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2186,7 +2184,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2208,7 +2206,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2230,7 +2228,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2252,7 +2250,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2274,7 +2272,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2296,7 +2294,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2318,7 +2316,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2340,7 +2338,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2362,7 +2360,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2384,7 +2382,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2406,7 +2404,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà mặt phố</t>
+          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2423,17 +2421,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -2445,17 +2443,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -2467,17 +2465,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -2489,17 +2487,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -2511,17 +2509,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -2533,17 +2531,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -2555,17 +2553,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -2577,17 +2575,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -2599,17 +2597,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -2621,17 +2619,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -2643,17 +2641,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -2665,17 +2663,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -2687,17 +2685,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -2709,17 +2707,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -2731,17 +2729,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -2753,17 +2751,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đất nền / Đất nền dự án</t>
+          <t xml:space="preserve">Thuê đất / Nhà xưởng / Kho bãi</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -2775,17 +2773,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -2797,17 +2795,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -2819,17 +2817,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -2841,17 +2839,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -2863,17 +2861,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -2885,17 +2883,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -2907,17 +2905,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -2929,17 +2927,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shophouse / Nhà phố thương mại</t>
+          <t xml:space="preserve">Căn hộ dịch vụ</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">ban</t>
+          <t xml:space="preserve">thue</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -2951,12 +2949,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2973,12 +2971,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2995,12 +2993,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3017,12 +3015,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3039,12 +3037,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3061,12 +3059,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3083,12 +3081,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3105,12 +3103,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chung cư</t>
+          <t xml:space="preserve">Văn phòng</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3127,12 +3125,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3149,12 +3147,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3171,12 +3169,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3193,12 +3191,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3215,12 +3213,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3237,12 +3235,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3259,12 +3257,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3281,12 +3279,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huế</t>
+          <t xml:space="preserve">Đà Nẵng</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nhà riêng</t>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3484,7 +3482,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3506,7 +3504,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3528,7 +3526,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3550,7 +3548,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3572,7 +3570,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3594,7 +3592,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3616,7 +3614,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3638,7 +3636,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mặt bằng / Cửa hàng bán lẻ</t>
+          <t xml:space="preserve">Căn hộ</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3647,6 +3645,710 @@
         </is>
       </c>
       <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà riêng</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thue</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà mặt phố</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huế</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhà biệt thự / Liền kề</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ban</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-Q3</t>
         </is>
